--- a/docs/downloads/04/tbl_other_act_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_marovoay_tous.xlsx
@@ -477,12 +477,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +489,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -621,12 +609,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -693,12 +675,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -747,12 +723,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -873,12 +843,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -890,12 +854,6 @@
         <is>
           <t>Éleveur</t>
         </is>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30">
-        <v>0.5</v>
       </c>
     </row>
     <row r="31">

--- a/docs/downloads/04/tbl_other_act_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,14 +384,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>310</v>
-      </c>
-      <c r="D2">
-        <v>56.9</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -402,14 +396,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
       <c r="D3">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="4">
@@ -420,14 +414,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="D4">
-        <v>1.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="5">
@@ -438,14 +432,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C5">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>22.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
@@ -456,14 +450,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C6">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="7">
@@ -474,8 +468,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>56</v>
+      </c>
+      <c r="D7">
+        <v>22.3</v>
       </c>
     </row>
     <row r="8">
@@ -486,26 +486,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>24</v>
-      </c>
-      <c r="D9">
-        <v>4.4</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -516,14 +516,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C10">
-        <v>241</v>
+        <v>15</v>
       </c>
       <c r="D10">
-        <v>58.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="11">
@@ -534,14 +534,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C11">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="D11">
-        <v>4.1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -552,14 +552,8 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>8</v>
-      </c>
-      <c r="D12">
-        <v>1.9</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -570,14 +564,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C13">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="D13">
-        <v>21.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="14">
@@ -595,7 +589,7 @@
         <v>37</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -606,26 +600,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>11.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C16">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D16">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="17">
@@ -636,14 +636,8 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>187</v>
-      </c>
-      <c r="D17">
-        <v>47.7</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -654,14 +648,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C18">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="D18">
-        <v>5.4</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="19">
@@ -672,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -684,14 +678,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C20">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="D20">
-        <v>34.7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="21">
@@ -709,7 +703,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>6.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="22">
@@ -720,26 +714,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>22</v>
+      </c>
+      <c r="D22">
+        <v>9.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="24">
@@ -750,14 +750,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C24">
-        <v>264</v>
+        <v>33</v>
       </c>
       <c r="D24">
-        <v>61.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -768,14 +768,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C25">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="D25">
-        <v>5.4</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="26">
@@ -786,14 +786,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C26">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -804,14 +804,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C27">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D27">
-        <v>16.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -829,7 +829,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>6.3</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="29">
@@ -840,38 +840,50 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>30</v>
+      </c>
+      <c r="D29">
+        <v>15.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>30</v>
+      </c>
+      <c r="D30">
+        <v>3.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C31">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D31">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="32">
@@ -882,14 +894,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C32">
-        <v>1002</v>
+        <v>419</v>
       </c>
       <c r="D32">
-        <v>56.4</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="33">
@@ -900,14 +912,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C33">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D33">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="34">
@@ -918,14 +930,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C34">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="D34">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="35">
@@ -936,14 +948,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C35">
-        <v>419</v>
+        <v>147</v>
       </c>
       <c r="D35">
-        <v>23.6</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="36">
@@ -954,68 +966,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C36">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="D36">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Pêcheur exploitant</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>6</v>
-      </c>
-      <c r="D37">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>7</v>
-      </c>
-      <c r="D38">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>80</v>
-      </c>
-      <c r="D39">
-        <v>4.5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_act_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">

--- a/docs/downloads/04/tbl_other_act_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -468,14 +468,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="C7">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>22.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="8">
@@ -486,26 +486,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bepako</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -516,14 +522,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>15</v>
-      </c>
-      <c r="D10">
-        <v>8.1</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -534,14 +534,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C11">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="D11">
-        <v>47</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="12">
@@ -552,8 +552,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>87</v>
+      </c>
+      <c r="D12">
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -564,14 +570,8 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>21</v>
-      </c>
-      <c r="D13">
-        <v>11.4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -582,14 +582,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C14">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="15">
@@ -600,43 +600,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D15">
-        <v>11.9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Madiromiongana</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D16">
-        <v>6.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Madiromiongana</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -648,14 +648,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C18">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>61.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -678,14 +678,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C20">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="D20">
-        <v>7.7</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="21">
@@ -696,14 +696,8 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>27</v>
-      </c>
-      <c r="D21">
-        <v>12.2</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -714,68 +708,62 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C22">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D22">
-        <v>9.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D23">
-        <v>5.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C24">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D24">
-        <v>17</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>71</v>
-      </c>
-      <c r="D25">
-        <v>36.6</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -786,14 +774,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="27">
@@ -804,14 +792,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C27">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D27">
-        <v>9.300000000000001</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -822,14 +810,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C28">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="D28">
-        <v>13.9</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="29">
@@ -840,86 +828,86 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C29">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>15.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C30">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D30">
-        <v>3.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="C31">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="D31">
-        <v>7.5</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C32">
-        <v>419</v>
+        <v>27</v>
       </c>
       <c r="D32">
-        <v>49.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C33">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="34">
@@ -930,14 +918,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C34">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D34">
-        <v>9.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="35">
@@ -948,14 +936,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C35">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="D35">
-        <v>17.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="36">
@@ -966,14 +954,104 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>419</v>
+      </c>
+      <c r="D36">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>18</v>
+      </c>
+      <c r="D37">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>80</v>
+      </c>
+      <c r="D38">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>76</v>
+      </c>
+      <c r="D39">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>147</v>
+      </c>
+      <c r="D40">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Services &amp; Autres</t>
         </is>
       </c>
-      <c r="C36">
-        <v>94</v>
-      </c>
-      <c r="D36">
-        <v>11</v>
+      <c r="C41">
+        <v>18</v>
+      </c>
+      <c r="D41">
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
